--- a/docs/VESMA_podklad_pre_MZI_experta.xlsx
+++ b/docs/VESMA_podklad_pre_MZI_experta.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <bookView visibility="visible" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Úvod" sheetId="1" state="visible" r:id="rId1"/>
@@ -562,6 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -570,203 +571,213 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">VESMA — podklad pre expertku na modrozelenú infraštruktúru</t>
-        </is>
-      </c>
-    </row>
+          <t>VESMA — podklad pre expertku na modrozelenú infraštruktúru</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VESMA je dotazníkový nástroj pre samosprávy. Pomáha nadšenému laikovi zorientovať sa v tom, čo</t>
+          <t>VESMA je dotazníkový nástroj pre samosprávy. Pomáha nadšenému laikovi zorientovať sa v tom, čo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sa v jeho areáli oplatí riešiť — v oblasti vody, energetiky a adaptácie na zmenu klímy.</t>
+          <t>sa v jeho areáli oplatí riešiť — v oblasti vody, energetiky a adaptácie na zmenu klímy.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nie je to projekt vodozádržných opatrení a ani sa tak netvári.</t>
-        </is>
-      </c>
-    </row>
+          <t>Nie je to projekt vodozádržných opatrení a ani sa tak netvári.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ČO UŽ JE ROZHODNUTÉ — NA TO SA NEPÝTAME</t>
+          <t>ČO UŽ JE ROZHODNUTÉ — NA TO SA NEPÝTAME</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skóre modrozelenej infraštruktúry sa počíta podľa metodiky KLIMASKEN (metodické listy B-GOV2,</t>
+          <t>Skóre modrozelenej infraštruktúry sa počíta podľa metodiky KLIMASKEN (metodické listy B-GOV2,</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">B-GOV3 a B-AD10). Metodika priniesla koeficienty povrchov, päťstupňovú škálu A – E aj výpočet</t>
+          <t>B-GOV3 a B-AD10). Metodika priniesla koeficienty povrchov, päťstupňovú škálu A – E aj výpočet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">potrebného objemu nádrže — teda väčšinu čísel, ktoré predtým v nástroji chýbali alebo boli</t>
+          <t>potrebného objemu nádrže — teda väčšinu čísel, ktoré predtým v nástroji chýbali alebo boli</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">odhadnuté. Zanikla aj zložka „potenciál zlepšenia", ktorá pridávala body za zlý stav.</t>
-        </is>
-      </c>
-    </row>
+          <t>odhadnuté. Zanikla aj zložka „potenciál zlepšenia", ktorá pridávala body za zlý stav.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prahy pre odporúčania (spevnená plocha nad 15 %, jazierko od 500 m², pokryvnosť korunami pod</t>
+          <t>Prahy pre odporúčania (spevnená plocha nad 15 %, jazierko od 500 m², pokryvnosť korunami pod</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 %) a ponuka opatrení prešli Vašou revíziou pravidiel v septembri 2026. Neotvárame ich znova.</t>
-        </is>
-      </c>
-    </row>
+          <t>30 %) a ponuka opatrení prešli Vašou revíziou pravidiel v septembri 2026. Neotvárame ich znova.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ČO ZOSTÁVA</t>
+          <t>ČO ZOSTÁVA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Šesť miest, kde metodika odpoveď nedáva a rozhodli sme sami alebo nechali hodnotu bez zdroja.</t>
+          <t>Šesť miest, kde metodika odpoveď nedáva a rozhodli sme sami alebo nechali hodnotu bez zdroja.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nevymýšľali sme si: na výstupe nie je vidieť, že hodnota je odhad, a nástroj pre samosprávy by</t>
+          <t>Nevymýšľali sme si: na výstupe nie je vidieť, že hodnota je odhad, a nástroj pre samosprávy by</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tým začal klamať sebavedomo.</t>
-        </is>
-      </c>
-    </row>
+          <t>tým začal klamať sebavedomo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Každý hárok je jedna tabuľka. Žlté bunky sú na vyplnenie, zelený riadok je vzor s formátom,</t>
+          <t>Každý hárok je jedna tabuľka. Žlté bunky sú na vyplnenie, zelený riadok je vzor s formátom,</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">aký očakávame — prepíšte ho alebo zmažte. Ostatné bunky sú kontext, netreba ich meniť.</t>
-        </is>
-      </c>
-    </row>
+          <t>aký očakávame — prepíšte ho alebo zmažte. Ostatné bunky sú kontext, netreba ich meniť.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ak niektorú hodnotu neviete podložiť zdrojom, nechajte ju prázdnu a napíšte to do poznámky.</t>
+          <t>Ak niektorú hodnotu neviete podložiť zdrojom, nechajte ju prázdnu a napíšte to do poznámky.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prázdna hodnota je pre nás lepší výsledok než odhad, ktorý sa bude tváriť ako fakt.</t>
-        </is>
-      </c>
-    </row>
+          <t>Prázdna hodnota je pre nás lepší výsledok než odhad, ktorý sa bude tváriť ako fakt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PREHĽAD HÁRKOV</t>
-        </is>
-      </c>
-    </row>
+          <t>PREHĽAD HÁRKOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Zaradenie povrchov — kontrola, ako sú otázky dotazníka namapované na kódy Klimaskenu. Štyri povrchy metodika nepozná a zaradili sme ich sami.</t>
+          <t>1. Zaradenie povrchov — kontrola, ako sú otázky dotazníka namapované na kódy Klimaskenu. Štyri povrchy metodika nepozná a zaradili sme ich sami.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Váhy komponentov — ako sa štyri komponenty skladajú do jedného skóre 0 – 100. Klimasken váhy medzi indikátormi nedáva, sú naše.</t>
+          <t>2. Váhy komponentov — ako sa štyri komponenty skladajú do jedného skóre 0 – 100. Klimasken váhy medzi indikátormi nedáva, sú naše.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Parametre akumulácie — vstupy výpočtu B-AD10. Väčšina je z metodiky, dva sme určili sami.</t>
+          <t>3. Parametre akumulácie — vstupy výpočtu B-AD10. Väčšina je z metodiky, dva sme určili sami a v jednom sa od metodiky odchyľujeme.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Čísla v odporúčaniach — štyri čísla, ktoré zostali mimo skóre a bez zdroja (napr. „zachytí 0,3 m³ na m² strechy ročne").</t>
+          <t>4. Čísla v odporúčaniach — štyri čísla, ktoré zostali mimo skóre a bez zdroja (napr. „zachytí 0,3 m³ na m² strechy ročne").</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. Ceny opatrení — orientačná cena a návratnosť 14 opatrení. Zdroj čísel nie je v nástroji zaznamenaný.</t>
+          <t>5. Ceny opatrení — orientačná cena a návratnosť 14 opatrení plus 3 nové pre obrábanú pôdu. Zdroj čísel nie je v nástroji zaznamenaný.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6. Otvorené rozhodnutia — tri otázky k porovnaniu areálov a k nevyužitému povodňovému riziku.</t>
-        </is>
-      </c>
-    </row>
+          <t>6. Otvorené rozhodnutia — tri otázky k porovnaniu areálov a k nevyužitému povodňovému riziku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEGENDA</t>
+          <t>LEGENDA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">žltá bunka = sem vpíšte hodnotu</t>
+          <t>žltá bunka = sem vpíšte hodnotu</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">zelený riadok = vzor s očakávaným formátom, prepíšte alebo zmažte</t>
+          <t>zelený riadok = vzor s očakávaným formátom, prepíšte alebo zmažte</t>
         </is>
       </c>
     </row>
@@ -781,6 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -793,81 +805,81 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Zaradenie povrchov do kódov Klimaskenu</t>
+          <t>1. Zaradenie povrchov do kódov Klimaskenu</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Načo to je: koeficient MZI sa počíta ako vážený priemer Σ(k · S) / Σ(S) — každá plocha vstupuje</t>
+          <t>Načo to je: koeficient MZI sa počíta ako vážený priemer Σ(k · S) / Σ(S) — každá plocha vstupuje</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">koeficientom k podľa svojho typu. Zaradenie teda priamo určuje výsledok aj stupeň A – E.</t>
+          <t>koeficientom k podľa svojho typu. Zaradenie teda priamo určuje výsledok aj stupeň A – E.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prosíme prejsť tabuľku a opraviť to, čo je zaradené zle. Riadky označené „mimo metodiky" sú tie,</t>
+          <t>Prosíme prejsť tabuľku a opraviť to, čo je zaradené zle. Riadky označené „mimo metodiky" sú tie,</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">kde Klimasken povrch nepozná a hodnotu sme určili my — tam čakáme odpoveď v každom prípade.</t>
+          <t>kde Klimasken povrch nepozná a hodnotu sme určili my — tam čakáme odpoveď v každom prípade.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Okolie budovy — metodický list B-GOV2</t>
+          <t>Okolie budovy — metodický list B-GOV2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Povrch alebo prvok (otázka vo VESMA)</t>
+          <t>Povrch alebo prvok (otázka vo VESMA)</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kód</t>
+          <t>Kód</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">k dnes</t>
+          <t>k dnes</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">k opravené</t>
+          <t>k opravené</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poznámka</t>
+          <t>Poznámka</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(vzor) Mlatový povrch</t>
+          <t>(vzor) Mlatový povrch</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -878,19 +890,19 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">súhlasím / opravujem na X, lebo…</t>
+          <t>súhlasím / opravujem na X, lebo…</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spevnená plocha (asfalt, betón, zámková dlažba)</t>
+          <t>Spevnená plocha (asfalt, betón, zámková dlažba)</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
@@ -902,12 +914,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mlatový povrch</t>
+          <t>Mlatový povrch</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
@@ -919,12 +931,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priepustný asfalt, priepustný betón, vodopriepustná dlažba, živica s kremičitým štrkom, Stered</t>
+          <t>Priepustný asfalt, priepustný betón, vodopriepustná dlažba, živica s kremičitým štrkom, Stered</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
@@ -936,12 +948,12 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pravidelne obrábaná pôda (hriadky, záhony, polia)</t>
+          <t>Pravidelne obrábaná pôda (hriadky, záhony, polia)</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
@@ -953,12 +965,12 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plnovegetačné tvárnice</t>
+          <t>Plnovegetačné tvárnice</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
@@ -970,12 +982,12 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byliny a trávnik</t>
+          <t>Byliny a trávnik</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">H</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
@@ -987,12 +999,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kry</t>
+          <t>Kry</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">L</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -1004,12 +1016,12 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stromy — zdravé vzrastlé</t>
+          <t>Stromy — zdravé vzrastlé</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">J</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
@@ -1021,12 +1033,12 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stromy — mladé A NEZDRAVÉ</t>
+          <t>Stromy — mladé A NEZDRAVÉ</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">K</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
@@ -1035,19 +1047,19 @@
       <c r="D19" s="12" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">nezdravé stromy hodnotíme rovnako ako mladé — je to primerané?</t>
+          <t>nezdravé stromy hodnotíme rovnako ako mladé — je to primerané?</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Podzemný prekoreniteľný priestor pre stromy</t>
+          <t>Podzemný prekoreniteľný priestor pre stromy</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
@@ -1059,12 +1071,12 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vsakovacia preliačina s regulovaným odtokom</t>
+          <t>Vsakovacia preliačina s regulovaným odtokom</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
@@ -1076,12 +1088,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dažďová záhrada, vsakovacia preliačina s bezpečnostným prepadom</t>
+          <t>Dažďová záhrada, vsakovacia preliačina s bezpečnostným prepadom</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
@@ -1093,12 +1105,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jazierko / mokraď</t>
+          <t>Jazierko / mokraď</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mimo metodiky (hodnotíme ako S)</t>
+          <t>mimo metodiky (hodnotíme ako S)</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
@@ -1107,19 +1119,19 @@
       <c r="D23" s="12" t="inlineStr"/>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">metodika jazierko nepozná — je plošný objekt HDV správne zaradenie?</t>
+          <t>metodika jazierko nepozná — je plošný objekt HDV správne zaradenie?</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polovegetačné tvárnice</t>
+          <t>Polovegetačné tvárnice</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mimo metodiky</t>
+          <t>mimo metodiky</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
@@ -1128,19 +1140,19 @@
       <c r="D24" s="12" t="inlineStr"/>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">naše zaradenie medzi kódy B a C</t>
+          <t>naše zaradenie medzi kódy B a C</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iný priepustný povrch</t>
+          <t>Iný priepustný povrch</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mimo metodiky</t>
+          <t>mimo metodiky</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
@@ -1149,19 +1161,19 @@
       <c r="D25" s="12" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">naše zaradenie medzi kódy B a C</t>
+          <t>naše zaradenie medzi kódy B a C</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nešpecifikovaný zvyšok polopriepustnej plochy</t>
+          <t>Nešpecifikovaný zvyšok polopriepustnej plochy</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mimo metodiky</t>
+          <t>mimo metodiky</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
@@ -1170,53 +1182,53 @@
       <c r="D26" s="12" t="inlineStr"/>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">keď používateľ nerozpíše celých 100 % typov povrchu</t>
+          <t>keď používateľ nerozpíše celých 100 % typov povrchu</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strechy a zvislé konštrukcie — metodický list B-GOV3</t>
+          <t>Strechy a zvislé konštrukcie — metodický list B-GOV3</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Povrch alebo prvok (otázka vo VESMA)</t>
+          <t>Povrch alebo prvok (otázka vo VESMA)</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kód</t>
+          <t>Kód</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">k dnes</t>
+          <t>k dnes</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">k opravené</t>
+          <t>k opravené</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poznámka</t>
+          <t>Poznámka</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strecha bez úprav</t>
+          <t>Strecha bez úprav</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">XX</t>
+          <t>XX</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
@@ -1228,12 +1240,12 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zelená stena, popínavé rastliny</t>
+          <t>Zelená stena, popínavé rastliny</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
@@ -1245,12 +1257,12 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extenzívna strešná záhrada na plochej streche</t>
+          <t>Extenzívna strešná záhrada na plochej streche</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
@@ -1262,12 +1274,12 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extenzívna strešná záhrada na šikmej streche</t>
+          <t>Extenzívna strešná záhrada na šikmej streche</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
@@ -1276,19 +1288,19 @@
       <c r="D33" s="12" t="inlineStr"/>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">metodika definuje E2 „od 35°", VESMA sem dáva aj strechy 16 – 35° — má pre ne platiť E1, E2, alebo hodnota medzi tým?</t>
+          <t>metodika definuje E2 „od 35°", VESMA sem dáva aj strechy 16 – 35° — má pre ne platiť E1, E2, alebo hodnota medzi tým?</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intenzívna strešná záhrada</t>
+          <t>Intenzívna strešná záhrada</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
@@ -1300,12 +1312,12 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modrá alebo modrozelená strecha</t>
+          <t>Modrá alebo modrozelená strecha</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
@@ -1317,12 +1329,12 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strecha so štrkovým zásypom</t>
+          <t>Strecha so štrkovým zásypom</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
@@ -1342,6 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1354,81 +1367,83 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Váhy komponentov MZI skóre</t>
+          <t>2. Váhy komponentov MZI skóre</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Načo to je: Klimasken hodnotí každý indikátor samostatne štítkom A – E, spoločnú váhu medzi</t>
+          <t>Načo to je: Klimasken hodnotí každý indikátor samostatne štítkom A – E, spoločnú váhu medzi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">indikátormi nedáva. VESMA ich skladá do jedného čísla 0 – 100 — a tie váhy sú naše, nie</t>
+          <t>indikátormi nedáva. VESMA ich skladá do jedného čísla 0 – 100 — a tie váhy sú naše, nie</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">z metodiky. Rozhodujú o tom, čo areál najviac potiahne hore alebo dole.</t>
-        </is>
-      </c>
-    </row>
+          <t>z metodiky. Rozhodujú o tom, čo areál najviac potiahne hore alebo dole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komponent, pre ktorý v dotazníku nie sú údaje, sa nezapočíta a skóre sa normalizuje cez zvyšné —</t>
+          <t>Komponent, pre ktorý v dotazníku nie sú údaje, sa nezapočíta a skóre sa normalizuje cez zvyšné —</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">areál tak nie je penalizovaný za neodpovedanú otázku.</t>
-        </is>
-      </c>
-    </row>
+          <t>areál tak nie je penalizovaný za neodpovedanú otázku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komponent</t>
+          <t>Komponent</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Čo meria</t>
+          <t>Čo meria</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Váha dnes</t>
+          <t>Váha dnes</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Váha potvrdená</t>
+          <t>Váha potvrdená</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poznámka</t>
+          <t>Poznámka</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(vzor) B-GOV2 — priepustnosť a zeleň areálu</t>
+          <t>(vzor) B-GOV2 — priepustnosť a zeleň areálu</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">vážený koeficient MZI plôch pozemkov</t>
+          <t>vážený koeficient MZI plôch pozemkov</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -1439,19 +1454,19 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">súhlasím / opravujem na X, lebo…</t>
+          <t>súhlasím / opravujem na X, lebo…</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">B-GOV3 — zeleň a retencia na budovách</t>
+          <t>B-GOV3 — zeleň a retencia na budovách</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">vážený koeficient MZI striech a zelených stien</t>
+          <t>vážený koeficient MZI striech a zelených stien</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
@@ -1463,12 +1478,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">B-AD10 — akumulácia zrážkovej vody</t>
+          <t>B-AD10 — akumulácia zrážkovej vody</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">podiel objemu nádrží na objeme, ktorý je pre areál optimálny</t>
+          <t>podiel objemu nádrží na objeme, ktorý je pre areál optimálny</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
@@ -1480,12 +1495,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zadržanie odtoku na mieste (doplnok VESMA)</t>
+          <t>Odtok zo spevnených plôch (doplnok VESMA)</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">podiel spevnených a polopriepustných plôch a striech, z ktorých voda ide do vsaku alebo retencie namiesto kanalizácie</t>
+          <t>podiel spevnených a polopriepustných plôch a striech, z ktorých voda ide do vsaku alebo retencie namiesto kanalizácie</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
@@ -1494,24 +1509,24 @@
       <c r="D13" s="12" t="inlineStr"/>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">nie je to indikátor Klimaskenu — pridali sme ho my</t>
+          <t>nie je to indikátor Klimaskenu — pridali sme ho my</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Má doplnok „zadržanie odtoku na mieste" v skóre vôbec byť?</t>
+          <t>Má doplnok „odtok zo spevnených plôch" v skóre vôbec byť?</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">bez neho by sa údaj o odvode vody, ktorý dotazník zbiera, do skóre nedostal</t>
+          <t>bez neho by sa údaj o odvode vody, ktorý dotazník zbiera, do skóre nedostal</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">áno, s váhou 15</t>
+          <t>áno, s váhou 15</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
@@ -1528,6 +1543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1540,21 +1556,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Parametre výpočtu akumulácie (B-AD10)</t>
+          <t>3. Parametre výpočtu akumulácie (B-AD10)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Načo to je: komponent porovnáva objem nádrží v areáli s objemom, ktorý je preň optimálny.</t>
+          <t>Načo to je: komponent porovnáva objem nádrží v areáli s objemom, ktorý je preň optimálny.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Potrebný objem sa počíta ako Vn = min(Vv; Vp), kde</t>
+          <t>Potrebný objem sa počíta ako Vn = min(Vv; Vp), kde</t>
         </is>
       </c>
     </row>
@@ -1582,41 +1598,41 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Väčšina parametrov je z metodického listu. Dva sme určili sami — sú v tabuľke označené.</t>
+          <t>Väčšina parametrov je z metodického listu. Dva sme určili sami — sú v tabuľke označené.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t>Parameter</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hodnota dnes</t>
+          <t>Hodnota dnes</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odkiaľ hodnota je</t>
+          <t>Odkiaľ hodnota je</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Potvrdená hodnota</t>
+          <t>Potvrdená hodnota</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poznámka</t>
+          <t>Poznámka</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(vzor) fs — koeficient odtoku strechy</t>
+          <t>(vzor) fs — koeficient odtoku strechy</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
@@ -1624,7 +1640,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAŠE ROZHODNUTIE — metodika ho odvodzuje z materiálu krytiny, VESMA má krytinu len ako voľný text, preto typická hodnota</t>
+          <t>NAŠE ROZHODNUTIE — metodika ho odvodzuje z materiálu krytiny, VESMA má krytinu len ako voľný text, preto typická hodnota</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
@@ -1632,14 +1648,14 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">súhlasím / pre bežné krytiny použite X</t>
+          <t>súhlasím / pre bežné krytiny použite X</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ff — účinnosť filtra mechanických nečistôt</t>
+          <t>ff — účinnosť filtra mechanických nečistôt</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
@@ -1647,7 +1663,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">metodika B-AD10</t>
+          <t>metodika B-AD10</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr"/>
@@ -1656,7 +1672,7 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sd — spotreba vody na osobu a deň (l)</t>
+          <t>Sd — spotreba vody na osobu a deň (l)</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
@@ -1664,7 +1680,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">metodika B-AD10</t>
+          <t>metodika B-AD10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr"/>
@@ -1673,7 +1689,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">R — koeficient využitia zrážkovej vody</t>
+          <t>R — koeficient využitia zrážkovej vody</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
@@ -1681,7 +1697,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">metodika B-AD10</t>
+          <t>metodika B-AD10</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
@@ -1690,7 +1706,7 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">z — koeficient optimálnej veľkosti nádrže</t>
+          <t>z — koeficient optimálnej veľkosti nádrže</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
@@ -1698,7 +1714,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">metodika B-AD10</t>
+          <t>metodika B-AD10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
@@ -1707,40 +1723,40 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">j — ročný úhrn zrážok (mm)</t>
+          <t>j — ročný úhrn zrážok (mm)</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">z Open-Meteo podľa adresy areálu</t>
+          <t>z Open-Meteo podľa adresy areálu</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dotazník VESMA</t>
+          <t>dotazník VESMA</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stačí ročný priemer z Open-Meteo, alebo treba iný zdroj?</t>
+          <t>stačí ročný priemer z Open-Meteo, alebo treba iný zdroj?</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">P — plocha striech (m²)</t>
+          <t>P — plocha striech (m²)</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">súčet pôdorysov všetkých budov areálu</t>
+          <t>súčet pôdorysov všetkých budov areálu</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dotazník VESMA</t>
+          <t>dotazník VESMA</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -1749,23 +1765,46 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">n — počet osôb v areáli</t>
+          <t>n — počet osôb v areáli</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">počet zamestnancov</t>
+          <t>počet zamestnancov</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAŠE ROZHODNUTIE</t>
+          <t>NAŠE ROZHODNUTIE</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">v škole to nie sú žiaci, v kultúrnom dome ani návštevníci — má sa použiť kapacita zariadenia alebo obsadenosť?</t>
+          <t>v škole to nie sú žiaci, v kultúrnom dome ani návštevníci — má sa použiť kapacita zariadenia alebo obsadenosť?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Keď nádrž nie je možné inštalovať</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>komponent sa do skóre nezapočíta</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>NAŠE ROZHODNUTIE — odchýlka od metodiky: B-AD10 zaraďuje objekt do najhoršej kategórie, my komponent vynechávame</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>skóre má viesť k rozhodnutiu, čo spraviť — komponent, na ktorý sa nedá reagovať, doň nepatrí. Je táto odchýlka v poriadku?</t>
         </is>
       </c>
     </row>
@@ -1780,6 +1819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1792,122 +1832,122 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Čísla v odporúčaniach, ktoré zostali bez zdroja</t>
+          <t>4. Čísla v odporúčaniach, ktoré zostali bez zdroja</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Načo to je: odporúčania sú to, čo si samospráva odnesie — text pri opatrení číta ako výsledok</t>
+          <t>Načo to je: odporúčania sú to, čo si samospráva odnesie — text pri opatrení číta ako výsledok</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">nástroja. Prahy, od ktorých sa opatrenie zobrazí, ste revidovali v septembri 2026 a nemeníme ich.</t>
+          <t>nástroja. Prahy, od ktorých sa opatrenie zobrazí, ste revidovali v septembri 2026 a nemeníme ich.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tieto štyri čísla revíziou neprešli a zdroj nemajú.</t>
+          <t>Tieto štyri čísla revíziou neprešli a zdroj nemajú.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Číslo</t>
+          <t>Číslo</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kde sa objaví a čo tvrdí</t>
+          <t>Kde sa objaví a čo tvrdí</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hodnota dnes</t>
+          <t>Hodnota dnes</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Potvrdená hodnota</t>
+          <t>Potvrdená hodnota</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poznámka</t>
+          <t>Poznámka</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(vzor) Zádrž štrkovej strechy</t>
+          <t>(vzor) Zádrž štrkovej strechy</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">koľko zrážky zadrží strecha so štrkovým zásypom</t>
+          <t>koľko zrážky zadrží strecha so štrkovým zásypom</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 % ročného úhrnu</t>
+          <t>20 % ročného úhrnu</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">vzor formátu — prepíšte alebo zmažte</t>
+          <t>vzor formátu — prepíšte alebo zmažte</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zádrž zelenej strechy</t>
+          <t>Zádrž zelenej strechy</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">veta „Potenciál zachytiť X m³ dažďovej vody ročne" pri zelenej streche — X = plocha plochých striech × 0,3</t>
+          <t>veta „Potenciál zachytiť X m³ dažďovej vody ročne" pri zelenej streche — X = plocha plochých striech × 0,3</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,3 m³ na m² za rok</t>
+          <t>0,3 m³ na m² za rok</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">pozri poznámku pod tabuľkou</t>
+          <t>pozri poznámku pod tabuľkou</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nahraditeľnosť spevnenej plochy</t>
+          <t>Nahraditeľnosť spevnenej plochy</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">veta „Potenciál nahradiť až X m² priepustným povrchom" pri priepustnej dlažbe — X je polovica spevnenej plochy areálu</t>
+          <t>veta „Potenciál nahradiť až X m² priepustným povrchom" pri priepustnej dlažbe — X je polovica spevnenej plochy areálu</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 %</t>
+          <t>50 %</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr"/>
@@ -1916,40 +1956,40 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minimálny objem retenčnej nádrže</t>
+          <t>Minimálny objem retenčnej nádrže</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">katalógový postup pri retenčnej nádrži: „min. 3 m³ pre rodinný dom"</t>
+          <t>katalógový postup pri retenčnej nádrži: „min. 3 m³ pre rodinný dom"</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 m³</t>
+          <t>3 m³</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr"/>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">výpočet B-AD10 už potrebný objem počíta — má tento údaj v katalógu vôbec zostať?</t>
+          <t>výpočet B-AD10 už potrebný objem počíta — má tento údaj v katalógu vôbec zostať?</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minimálna plocha jazierka</t>
+          <t>Minimálna plocha jazierka</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">katalógový postup pri jazierku: „min. 30 – 50 m² plochy pozemku"</t>
+          <t>katalógový postup pri jazierku: „min. 30 – 50 m² plochy pozemku"</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 – 50 m²</t>
+          <t>30 – 50 m²</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr"/>
@@ -1958,35 +1998,35 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">POZNÁMKA K ZÁDRŽI ZELENEJ STRECHY</t>
+          <t>POZNÁMKA K ZÁDRŽI ZELENEJ STRECHY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pri koeficiente 0,3 v prvom riadku tabuľky nesedia jednotky —</t>
+          <t>Pri koeficiente 0,3 v prvom riadku tabuľky nesedia jednotky —</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">z m² vyjde m³ za rok bez toho, aby do výpočtu vstúpili zrážky. Po zavedení metodiky vieme</t>
+          <t>z m² vyjde m³ za rok bez toho, aby do výpočtu vstúpili zrážky. Po zavedení metodiky vieme</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">zachytenú vodu počítať poriadne (Q = j · P · fs · ff), takže nám stačí podiel ročného úhrnu,</t>
+          <t>zachytenú vodu počítať poriadne (Q = j · P · fs · ff), takže nám stačí podiel ročného úhrnu,</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ktorý extenzívna zelená strecha zadrží. Ak taký údaj nie je, vetu radšej zrušíme.</t>
+          <t>ktorý extenzívna zelená strecha zadrží. Ak taký údaj nie je, vetu radšej zrušíme.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2014,130 +2055,130 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. Ceny a návratnosť opatrení modrozelenej infraštruktúry</t>
+          <t>5. Ceny a návratnosť opatrení modrozelenej infraštruktúry</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Načo to je: pri každom odporúčanom opatrení VESMA ukáže orientačnú cenu a návratnosť.</t>
+          <t>Načo to je: pri každom odporúčanom opatrení VESMA ukáže orientačnú cenu a návratnosť.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">V nástroji nie je zaznamenané, odkiaľ tie čísla pochádzajú.</t>
+          <t>V nástroji nie je zaznamenané, odkiaľ tie čísla pochádzajú.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Druhá vec: pri viacerých opatreniach nie je zrejmé, čo má „návratnosť" znamenať. Dažďová</t>
+          <t>Druhá vec: pri viacerých opatreniach nie je zrejmé, čo má „návratnosť" znamenať. Dažďová</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">záhrada ani kvitnúca lúka nič nezarábajú — nanajvýš šetria údržbu alebo stočné. Tam, kde</t>
+          <t>záhrada ani kvitnúca lúka nič nezarábajú — nanajvýš šetria údržbu alebo stočné. Tam, kde</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">finančná návratnosť nedáva zmysel, prosím napíšte, čo tam má stáť namiesto nej (napríklad</t>
+          <t>finančná návratnosť nedáva zmysel, prosím napíšte, čo tam má stáť namiesto nej (napríklad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">životnosť, alebo „bez priamej finančnej návratnosti").</t>
+          <t>životnosť, alebo „bez priamej finančnej návratnosti").</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opatrenie</t>
+          <t>Opatrenie</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cena dnes</t>
+          <t>Cena dnes</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Návratnosť dnes</t>
+          <t>Návratnosť dnes</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cena potvrdená</t>
+          <t>Cena potvrdená</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Návratnosť potvrdená / čo tam má stáť</t>
+          <t>Návratnosť potvrdená / čo tam má stáť</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poznámka / zdroj</t>
+          <t>Poznámka / zdroj</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(vzor) Dažďový sud 300 l</t>
+          <t>(vzor) Dažďový sud 300 l</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 – 300 EUR</t>
+          <t>50 – 300 EUR</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 – 3 roky</t>
+          <t>1 – 3 roky</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">80 – 250 EUR</t>
+          <t>80 – 250 EUR</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 – 4 roky pri polievaní záhrady</t>
+          <t>2 – 4 roky pri polievaní záhrady</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cenník dodávateľov 2026</t>
+          <t>cenník dodávateľov 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retenčná / akumulačná nádrž na dažďovú vodu</t>
+          <t>Retenčná / akumulačná nádrž na dažďovú vodu</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 000 – 8 000 EUR (podľa objemu)</t>
+          <t>2 000 – 8 000 EUR (podľa objemu)</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 – 10 rokov</t>
+          <t>5 – 10 rokov</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr"/>
@@ -2147,17 +2188,17 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dažďová záhrada</t>
+          <t>Dažďová záhrada</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">500 – 3 000 EUR</t>
+          <t>500 – 3 000 EUR</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 – 5 rokov</t>
+          <t>3 – 5 rokov</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr"/>
@@ -2167,17 +2208,17 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vsakovací rigol / jama</t>
+          <t>Vsakovací rigol / jama</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 500 – 5 000 EUR</t>
+          <t>1 500 – 5 000 EUR</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 – 8 rokov</t>
+          <t>5 – 8 rokov</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
@@ -2187,17 +2228,17 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zelená strecha (extenzívna)</t>
+          <t>Zelená strecha (extenzívna)</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">40 – 80 EUR/m²</t>
+          <t>40 – 80 EUR/m²</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 – 15 rokov</t>
+          <t>10 – 15 rokov</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
@@ -2207,17 +2248,17 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zelená strecha (intenzívna)</t>
+          <t>Zelená strecha (intenzívna)</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">80 – 200 EUR/m²</t>
+          <t>80 – 200 EUR/m²</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 – 25 rokov</t>
+          <t>15 – 25 rokov</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
@@ -2227,17 +2268,17 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priepustná / zatrávňovacia dlažba</t>
+          <t>Priepustná / zatrávňovacia dlažba</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 – 60 EUR/m²</t>
+          <t>25 – 60 EUR/m²</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 – 12 rokov</t>
+          <t>8 – 12 rokov</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -2247,17 +2288,17 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Výsadba stromov (tieňové)</t>
+          <t>Výsadba stromov (tieňové)</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 – 500 EUR/strom</t>
+          <t>50 – 500 EUR/strom</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 – 7 rokov</t>
+          <t>3 – 7 rokov</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
@@ -2267,17 +2308,17 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kvitnúca lúka namiesto trávnika</t>
+          <t>Kvitnúca lúka namiesto trávnika</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 – 10 EUR/m²</t>
+          <t>3 – 10 EUR/m²</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 – 3 roky</t>
+          <t>1 – 3 roky</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
@@ -2287,17 +2328,17 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vertikálna zeleň (zelená stena)</t>
+          <t>Vertikálna zeleň (zelená stena)</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">100 – 500 EUR/m² (modulový systém)</t>
+          <t>100 – 500 EUR/m² (modulový systém)</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 – 15 rokov</t>
+          <t>8 – 15 rokov</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
@@ -2307,17 +2348,17 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dažďový sud / zásobník</t>
+          <t>Dažďový sud / zásobník</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 – 300 EUR</t>
+          <t>50 – 300 EUR</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 – 3 roky</t>
+          <t>1 – 3 roky</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
@@ -2327,17 +2368,17 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odvedenie zrážkových vôd mimo kanalizáciu</t>
+          <t>Odvedenie zrážkových vôd mimo kanalizáciu</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">500 – 2 000 EUR</t>
+          <t>500 – 2 000 EUR</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 – 5 rokov</t>
+          <t>3 – 5 rokov</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr"/>
@@ -2347,17 +2388,17 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jazierko / vytvorená mokraď</t>
+          <t>Jazierko / vytvorená mokraď</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 000 – 20 000 EUR (podľa veľkosti)</t>
+          <t>3 000 – 20 000 EUR (podľa veľkosti)</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 – 20 rokov</t>
+          <t>10 – 20 rokov</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
@@ -2367,17 +2408,17 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Podzemné vsakovanie (tunel / studňa)</t>
+          <t>Podzemné vsakovanie (tunel / studňa)</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 000 – 15 000 EUR (podľa systému a hĺbky)</t>
+          <t>2 000 – 15 000 EUR (podľa systému a hĺbky)</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 – 15 rokov</t>
+          <t>8 – 15 rokov</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr"/>
@@ -2387,22 +2428,94 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zachytenie dažďovej vody do nádob</t>
+          <t>Zachytenie dažďovej vody do nádob</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">200 – 3 000 EUR</t>
+          <t>200 – 3 000 EUR</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 – 5 rokov</t>
+          <t>2 – 5 rokov</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr"/>
       <c r="F25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Mulčovanie obrábanej pôdy</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>NÁVRH: 1 – 4 EUR/m² (pri vlastnej štiepke takmer bez nákladov)</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>NÁVRH: do 1 roka (úspora zálievky a odburiňovania)</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>nové opatrenie, zatiaľ nie je v katalógu (issue #200) — hodnoty sú náš návrh</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Krycie plodiny a zelené hnojenie</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>NÁVRH: 0,05 – 0,20 EUR/m² (osivo)</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>NÁVRH: 1 – 2 sezóny (úspora hnojív)</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>nové opatrenie, zatiaľ nie je v katalógu (issue #200) — hodnoty sú náš návrh</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Obmedzenie orby (minimalizačné obrábanie)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>NÁVRH: pri službe porovnateľné s orbou; vlastná technika rádovo tisíce EUR</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>NÁVRH: 2 – 5 rokov</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>nové opatrenie, zatiaľ nie je v katalógu (issue #200) — hodnoty sú náš návrh</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2415,6 +2528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -2426,77 +2540,77 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">6. Otvorené rozhodnutia — nejde o číslo, ale o pravidlo</t>
+          <t>6. Otvorené rozhodnutia — nejde o číslo, ale o pravidlo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tri miesta mimo skóre, kde VESMA niečo zbiera alebo počíta a nie je zrejmé, či je to tak správne.</t>
+          <t>Tri miesta mimo skóre, kde VESMA niečo zbiera alebo počíta a nie je zrejmé, či je to tak správne.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tu nečakáme hodnotu, ale rozhodnutie — stačí veta.</t>
+          <t>Tu nečakáme hodnotu, ale rozhodnutie — stačí veta.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otázka</t>
+          <t>Otázka</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ako to je dnes</t>
+          <t>Ako to je dnes</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rozhodnutie</t>
+          <t>Rozhodnutie</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poznámka</t>
+          <t>Poznámka</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(vzor) Otázka</t>
+          <t>(vzor) Otázka</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stav v nástroji</t>
+          <t>stav v nástroji</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">áno / nie / inak, a ako</t>
+          <t>áno / nie / inak, a ako</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">vzor formátu — prepíšte alebo zmažte</t>
+          <t>vzor formátu — prepíšte alebo zmažte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Má voda odvedená do delenej zrážkovej kanalizácie vážiť rovnako ako voda do jednotnej stokovej siete?</t>
+          <t>Má voda odvedená do delenej zrážkovej kanalizácie vážiť rovnako ako voda do jednotnej stokovej siete?</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pri porovnaní areálov sa tri polia (jednotná, splašková, zrážková) sčítavajú do jednej hodnoty a vážia rovnako — 7 (sucho), 5 (horúčavy), 10 (voda). V skóre podľa Klimaskenu sa všetky tri rovnako počítajú ako „nezadržané".</t>
+          <t>Pri porovnaní areálov sa tri polia (jednotná, splašková, zrážková) sčítavajú do jednej hodnoty a vážia rovnako — 7 (sucho), 5 (horúčavy), 10 (voda). V skóre podľa Klimaskenu sa všetky tri rovnako počítajú ako „nezadržané".</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr"/>
@@ -2505,12 +2619,12 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ako má do hodnotenia vstúpiť povodňové riziko budovy?</t>
+          <t>Ako má do hodnotenia vstúpiť povodňové riziko budovy?</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VESMA ho zisťuje na stupnici 1 – 5 a vie ho načítať z máp SVP, ale nepoužíva ho v skóre, v odporúčaniach ani pri porovnaní areálov.</t>
+          <t>VESMA ho zisťuje na stupnici 1 – 5 a vie ho načítať z máp SVP, ale nepoužíva ho v skóre, v odporúčaniach ani pri porovnaní areálov.</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr"/>
@@ -2519,12 +2633,12 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Platia váhy 15 parametrov MZI pri porovnaní areálov aj naďalej?</t>
+          <t>Platia váhy 15 parametrov MZI pri porovnaní areálov aj naďalej?</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pochádzajú z tabuľky „MZI — spoločná dohoda" (august 2026). Zmenil sa im jeden vstup: pravidelne obrábaná pôda sa už nezapočítava do potenciálu na výsadbu stromov.</t>
+          <t>Pochádzajú z tabuľky „MZI — spoločná dohoda" (august 2026). Zmenil sa im jeden vstup: pravidelne obrábaná pôda sa už nezapočítava do potenciálu na výsadbu stromov.</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr"/>

--- a/docs/VESMA_podklad_pre_MZI_experta.xlsx
+++ b/docs/VESMA_podklad_pre_MZI_experta.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <bookView visibility="visible" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Úvod" sheetId="1" state="visible" r:id="rId1"/>
@@ -562,7 +562,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -571,213 +570,217 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VESMA — podklad pre expertku na modrozelenú infraštruktúru</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t xml:space="preserve">VESMA — podklad pre expertku na modrozelenú infraštruktúru</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>VESMA je dotazníkový nástroj pre samosprávy. Pomáha nadšenému laikovi zorientovať sa v tom, čo</t>
+          <t xml:space="preserve">VESMA je dotazníkový nástroj pre samosprávy. Pomáha nadšenému laikovi zorientovať sa v tom, čo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>sa v jeho areáli oplatí riešiť — v oblasti vody, energetiky a adaptácie na zmenu klímy.</t>
+          <t xml:space="preserve">sa v jeho areáli oplatí riešiť — v oblasti vody, energetiky a adaptácie na zmenu klímy.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Nie je to projekt vodozádržných opatrení a ani sa tak netvári.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+          <t xml:space="preserve">Nie je to projekt vodozádržných opatrení a ani sa tak netvári.</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ČO UŽ JE ROZHODNUTÉ — NA TO SA NEPÝTAME</t>
+          <t xml:space="preserve">ČO UŽ JE ROZHODNUTÉ — NA TO SA NEPÝTAME</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Skóre modrozelenej infraštruktúry sa počíta podľa metodiky KLIMASKEN (metodické listy B-GOV2,</t>
+          <t xml:space="preserve">Skóre modrozelenej infraštruktúry sa počíta podľa metodiky KLIMASKEN (metodické listy B-GOV2,</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>B-GOV3 a B-AD10). Metodika priniesla koeficienty povrchov, päťstupňovú škálu A – E aj výpočet</t>
+          <t xml:space="preserve">B-GOV3 a B-AD10). Metodika priniesla koeficienty povrchov, päťstupňovú škálu A – E aj výpočet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>potrebného objemu nádrže — teda väčšinu čísel, ktoré predtým v nástroji chýbali alebo boli</t>
+          <t xml:space="preserve">potrebného objemu nádrže — teda väčšinu čísel, ktoré predtým v nástroji chýbali alebo boli</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>odhadnuté. Zanikla aj zložka „potenciál zlepšenia", ktorá pridávala body za zlý stav.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t xml:space="preserve">odhadnuté. Zanikla aj zložka „potenciál zlepšenia", ktorá pridávala body za zlý stav.</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Prahy pre odporúčania (spevnená plocha nad 15 %, jazierko od 500 m², pokryvnosť korunami pod</t>
+          <t xml:space="preserve">Prahy pre odporúčania (spevnená plocha nad 15 %, jazierko od 500 m², pokryvnosť korunami pod</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>30 %) a ponuka opatrení prešli Vašou revíziou pravidiel v septembri 2026. Neotvárame ich znova.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t xml:space="preserve">30 %) a ponuka opatrení prešli Vašou revíziou pravidiel v septembri 2026. Neotvárame ich znova.</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>ČO ZOSTÁVA</t>
+          <t xml:space="preserve">ČO ZOSTÁVA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Šesť miest, kde metodika odpoveď nedáva a rozhodli sme sami alebo nechali hodnotu bez zdroja.</t>
+          <t xml:space="preserve">Šesť miest, kde metodika odpoveď nedáva a rozhodli sme sami alebo nechali hodnotu bez zdroja.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Nevymýšľali sme si: na výstupe nie je vidieť, že hodnota je odhad, a nástroj pre samosprávy by</t>
+          <t xml:space="preserve">Nevymýšľali sme si: na výstupe nie je vidieť, že hodnota je odhad, a nástroj pre samosprávy by</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>tým začal klamať sebavedomo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
+          <t xml:space="preserve">tým začal klamať sebavedomo.</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Každý hárok je jedna tabuľka. Žlté bunky sú na vyplnenie, zelený riadok je vzor s formátom,</t>
+          <t xml:space="preserve">Každý hárok je jedna tabuľka. Žlté bunky sú na vyplnenie, zelený riadok je vzor s formátom,</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>aký očakávame — prepíšte ho alebo zmažte. Ostatné bunky sú kontext, netreba ich meniť.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+          <t xml:space="preserve">aký očakávame — prepíšte ho alebo zmažte. Ostatné bunky sú kontext, netreba ich meniť.</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Ak niektorú hodnotu neviete podložiť zdrojom, nechajte ju prázdnu a napíšte to do poznámky.</t>
+          <t xml:space="preserve">Ak niektorú hodnotu neviete podložiť zdrojom, nechajte ju prázdnu a napíšte to do poznámky.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Prázdna hodnota je pre nás lepší výsledok než odhad, ktorý sa bude tváriť ako fakt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+          <t xml:space="preserve">Prázdna hodnota je pre nás lepší výsledok než odhad, ktorý sa bude tváriť ako fakt.</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>PREHĽAD HÁRKOV</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>1. Zaradenie povrchov — kontrola, ako sú otázky dotazníka namapované na kódy Klimaskenu. Štyri povrchy metodika nepozná a zaradili sme ich sami.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>2. Váhy komponentov — ako sa štyri komponenty skladajú do jedného skóre 0 – 100. Klimasken váhy medzi indikátormi nedáva, sú naše.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>3. Parametre akumulácie — vstupy výpočtu B-AD10. Väčšina je z metodiky, dva sme určili sami a v jednom sa od metodiky odchyľujeme.</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kódy M1 až M8 pri hárkoch odkazujú na register chýbajúcich hodnôt (docs/chybajuce-hodnoty.md),</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kde je pri každej hodnote stav a miesto v kóde. Vaše odpovede sa doň prepíšu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREHĽAD HÁRKOV</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>4. Čísla v odporúčaniach — štyri čísla, ktoré zostali mimo skóre a bez zdroja (napr. „zachytí 0,3 m³ na m² strechy ročne").</t>
+          <t xml:space="preserve">1. Zaradenie povrchov (M2) — kontrola, ako sú otázky dotazníka namapované na kódy Klimaskenu. Štyri zaradenia metodika nepokrýva a rozhodli sme ich sami.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>5. Ceny opatrení — orientačná cena a návratnosť 14 opatrení plus 3 nové pre obrábanú pôdu. Zdroj čísel nie je v nástroji zaznamenaný.</t>
+          <t xml:space="preserve">2. Váhy komponentov (M1) — ako sa štyri komponenty skladajú do jedného skóre 0 – 100. Klimasken váhy medzi indikátormi nedáva, sú naše.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>6. Otvorené rozhodnutia — tri otázky k porovnaniu areálov a k nevyužitému povodňovému riziku.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>žltá bunka = sem vpíšte hodnotu</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>zelený riadok = vzor s očakávaným formátom, prepíšte alebo zmažte</t>
+          <t xml:space="preserve">3. Parametre akumulácie (M3, M4) — vstupy výpočtu B-AD10. Väčšina je z metodiky, tri veci sme rozhodli sami vrátane jednej odchýlky od metodiky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Čísla v odporúčaniach (M5) — štyri čísla, ktoré zostali mimo skóre a bez zdroja (napr. „zachytí 0,3 m³ na m² strechy ročne").</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. Ceny opatrení (M6, M8) — cena a návratnosť 14 opatrení v katalógu a troch, ktoré čakajú na potvrdenie, aby sa mohli pridať.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Otvorené rozhodnutia (M7) — tri otázky k porovnaniu areálov a k nevyužitému povodňovému riziku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEGENDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">žltá bunka = sem vpíšte hodnotu</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zelený riadok = vzor s očakávaným formátom, prepíšte alebo zmažte</t>
         </is>
       </c>
     </row>
@@ -792,7 +795,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -805,176 +807,129 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>1. Zaradenie povrchov do kódov Klimaskenu</t>
+          <t xml:space="preserve">1. Zaradenie povrchov do kódov Klimaskenu</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Načo to je: koeficient MZI sa počíta ako vážený priemer Σ(k · S) / Σ(S) — každá plocha vstupuje</t>
+          <t xml:space="preserve">Načo to je: koeficient MZI sa počíta ako vážený priemer Σ(k · S) / Σ(S) — každá plocha vstupuje</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>koeficientom k podľa svojho typu. Zaradenie teda priamo určuje výsledok aj stupeň A – E.</t>
+          <t xml:space="preserve">koeficientom k podľa svojho typu. Zaradenie teda priamo určuje výsledok aj stupeň A – E.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Prosíme prejsť tabuľku a opraviť to, čo je zaradené zle. Riadky označené „mimo metodiky" sú tie,</t>
+          <t xml:space="preserve">Prosíme prejsť tabuľku a opraviť to, čo je zaradené zle. Riadky označené „mimo metodiky" sú tie,</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>kde Klimasken povrch nepozná a hodnotu sme určili my — tam čakáme odpoveď v každom prípade.</t>
+          <t xml:space="preserve">kde Klimasken povrch nepozná a hodnotu sme určili my — tam čakáme odpoveď v každom prípade.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Okolie budovy — metodický list B-GOV2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Povrch alebo prvok (otázka vo VESMA)</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Kód</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>k dnes</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>k opravené</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Poznámka</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tip: vo výsledkoch areálu je pri každom komponente tlačidlo „Zobraziť výpočet". Otvorí tabuľku</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v tvare metodických listov (povrch, kód, výmera, koeficient, príspevok) a dá sa skopírovať do</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>(vzor) Mlatový povrch</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excelu, takže zaradenie si viete overiť priamo na konkrétnom areáli.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Okolie budovy — metodický list B-GOV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Povrch alebo prvok (otázka vo VESMA)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kód</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">k dnes</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">k opravené</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(vzor) Mlatový povrch</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D14" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>súhlasím / opravujem na X, lebo…</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Spevnená plocha (asfalt, betón, zámková dlažba)</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12" t="inlineStr"/>
-      <c r="E11" s="12" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Mlatový povrch</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D12" s="12" t="inlineStr"/>
-      <c r="E12" s="12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Priepustný asfalt, priepustný betón, vodopriepustná dlažba, živica s kremičitým štrkom, Stered</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D13" s="12" t="inlineStr"/>
-      <c r="E13" s="12" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Pravidelne obrábaná pôda (hriadky, záhony, polia)</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="12" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">súhlasím / opravujem na X, lebo…</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Plnovegetačné tvárnice</t>
+          <t xml:space="preserve">Spevnená plocha (asfalt, betón, zámková dlažba)</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
       <c r="E15" s="12" t="inlineStr"/>
@@ -982,16 +937,16 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Byliny a trávnik</t>
+          <t xml:space="preserve">Mlatový povrch</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
       <c r="E16" s="12" t="inlineStr"/>
@@ -999,12 +954,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Kry</t>
+          <t xml:space="preserve">Priepustný asfalt, priepustný betón, vodopriepustná dlažba, živica s kremičitým štrkom, Stered</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -1016,16 +971,16 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Stromy — zdravé vzrastlé</t>
+          <t xml:space="preserve">Pravidelne obrábaná pôda (hriadky, záhony, polia)</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>J</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
       <c r="E18" s="12" t="inlineStr"/>
@@ -1033,37 +988,33 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Stromy — mladé A NEZDRAVÉ</t>
+          <t xml:space="preserve">Plnovegetačné tvárnice</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>K</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
         <v>0.4</v>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>nezdravé stromy hodnotíme rovnako ako mladé — je to primerané?</t>
-        </is>
-      </c>
+      <c r="E19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Podzemný prekoreniteľný priestor pre stromy</t>
+          <t xml:space="preserve">Byliny a trávnik</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">H</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
       <c r="E20" s="12" t="inlineStr"/>
@@ -1071,16 +1022,16 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Vsakovacia preliačina s regulovaným odtokom</t>
+          <t xml:space="preserve">Kry</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t xml:space="preserve">L</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
       <c r="E21" s="12" t="inlineStr"/>
@@ -1088,12 +1039,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Dažďová záhrada, vsakovacia preliačina s bezpečnostným prepadom</t>
+          <t xml:space="preserve">Stromy — zdravé vzrastlé</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t xml:space="preserve">J</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
@@ -1105,206 +1056,206 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Jazierko / mokraď</t>
+          <t xml:space="preserve">Stromy — mladé A NEZDRAVÉ</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>mimo metodiky (hodnotíme ako S)</t>
+          <t xml:space="preserve">K</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>metodika jazierko nepozná — je plošný objekt HDV správne zaradenie?</t>
+          <t xml:space="preserve">nezdravé stromy hodnotíme rovnako ako mladé — je to primerané?</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Polovegetačné tvárnice</t>
+          <t xml:space="preserve">Podzemný prekoreniteľný priestor pre stromy</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>mimo metodiky</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>naše zaradenie medzi kódy B a C</t>
-        </is>
-      </c>
+      <c r="E24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Iný priepustný povrch</t>
+          <t xml:space="preserve">Vsakovacia preliačina s regulovaným odtokom</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>mimo metodiky</t>
+          <t xml:space="preserve">R</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D25" s="12" t="inlineStr"/>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>naše zaradenie medzi kódy B a C</t>
-        </is>
-      </c>
+      <c r="E25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Nešpecifikovaný zvyšok polopriepustnej plochy</t>
+          <t xml:space="preserve">Dažďová záhrada, vsakovacia preliačina s bezpečnostným prepadom</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>mimo metodiky</t>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr"/>
+      <c r="E26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jazierko / mokraď</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mimo metodiky (hodnotíme ako S)</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr"/>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodika jazierko nepozná — je plošný objekt HDV správne zaradenie?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polovegetačné tvárnice</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mimo metodiky</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="D26" s="12" t="inlineStr"/>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>keď používateľ nerozpíše celých 100 % typov povrchu</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Strechy a zvislé konštrukcie — metodický list B-GOV3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Povrch alebo prvok (otázka vo VESMA)</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Kód</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>k dnes</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>k opravené</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>Poznámka</t>
+      <c r="D28" s="12" t="inlineStr"/>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">naše zaradenie medzi kódy B a C</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iný priepustný povrch</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mimo metodiky</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr"/>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">naše zaradenie medzi kódy B a C</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Strecha bez úprav</t>
+          <t xml:space="preserve">Nešpecifikovaný zvyšok polopriepustnej plochy</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t xml:space="preserve">mimo metodiky</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Zelená stena, popínavé rastliny</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr"/>
-      <c r="E31" s="12" t="inlineStr"/>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keď používateľ nerozpíše celých 100 % typov povrchu</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Extenzívna strešná záhrada na plochej streche</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D32" s="12" t="inlineStr"/>
-      <c r="E32" s="12" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Extenzívna strešná záhrada na šikmej streche</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>metodika definuje E2 „od 35°", VESMA sem dáva aj strechy 16 – 35° — má pre ne platiť E1, E2, alebo hodnota medzi tým?</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strechy a zvislé konštrukcie — metodický list B-GOV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Povrch alebo prvok (otázka vo VESMA)</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kód</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">k dnes</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">k opravené</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poznámka</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>Intenzívna strešná záhrada</t>
+          <t xml:space="preserve">Strecha bez úprav</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t xml:space="preserve">XX</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D34" s="12" t="inlineStr"/>
       <c r="E34" s="12" t="inlineStr"/>
@@ -1312,16 +1263,16 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>Modrá alebo modrozelená strecha</t>
+          <t xml:space="preserve">Zelená stena, popínavé rastliny</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D35" s="12" t="inlineStr"/>
       <c r="E35" s="12" t="inlineStr"/>
@@ -1329,19 +1280,91 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>Strecha so štrkovým zásypom</t>
+          <t xml:space="preserve">Extenzívna strešná záhrada na plochej streche</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D36" s="12" t="inlineStr"/>
       <c r="E36" s="12" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extenzívna strešná záhrada na šikmej streche</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E2</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr"/>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodika definuje E2 „od 35°", VESMA sem dáva aj strechy 16 – 35° — má pre ne platiť E1, E2, alebo hodnota medzi tým?</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intenzívna strešná záhrada</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr"/>
+      <c r="E38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modrá alebo modrozelená strecha</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr"/>
+      <c r="E39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strecha so štrkovým zásypom</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr"/>
+      <c r="E40" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1354,7 +1377,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1367,83 +1389,81 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2. Váhy komponentov MZI skóre</t>
+          <t xml:space="preserve">2. Váhy komponentov MZI skóre</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Načo to je: Klimasken hodnotí každý indikátor samostatne štítkom A – E, spoločnú váhu medzi</t>
+          <t xml:space="preserve">Načo to je: Klimasken hodnotí každý indikátor samostatne štítkom A – E, spoločnú váhu medzi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>indikátormi nedáva. VESMA ich skladá do jedného čísla 0 – 100 — a tie váhy sú naše, nie</t>
+          <t xml:space="preserve">indikátormi nedáva. VESMA ich skladá do jedného čísla 0 – 100 — a tie váhy sú naše, nie</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>z metodiky. Rozhodujú o tom, čo areál najviac potiahne hore alebo dole.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+          <t xml:space="preserve">z metodiky. Rozhodujú o tom, čo areál najviac potiahne hore alebo dole.</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Komponent, pre ktorý v dotazníku nie sú údaje, sa nezapočíta a skóre sa normalizuje cez zvyšné —</t>
+          <t xml:space="preserve">Komponent, pre ktorý v dotazníku nie sú údaje, sa nezapočíta a skóre sa normalizuje cez zvyšné —</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>areál tak nie je penalizovaný za neodpovedanú otázku.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t xml:space="preserve">areál tak nie je penalizovaný za neodpovedanú otázku.</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Komponent</t>
+          <t xml:space="preserve">Komponent</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Čo meria</t>
+          <t xml:space="preserve">Čo meria</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Váha dnes</t>
+          <t xml:space="preserve">Váha dnes</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Váha potvrdená</t>
+          <t xml:space="preserve">Váha potvrdená</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Poznámka</t>
+          <t xml:space="preserve">Poznámka</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>(vzor) B-GOV2 — priepustnosť a zeleň areálu</t>
+          <t xml:space="preserve">(vzor) B-GOV2 — priepustnosť a zeleň areálu</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>vážený koeficient MZI plôch pozemkov</t>
+          <t xml:space="preserve">vážený koeficient MZI plôch pozemkov</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -1454,19 +1474,19 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>súhlasím / opravujem na X, lebo…</t>
+          <t xml:space="preserve">súhlasím / opravujem na X, lebo…</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>B-GOV3 — zeleň a retencia na budovách</t>
+          <t xml:space="preserve">B-GOV3 — zeleň a retencia na budovách</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>vážený koeficient MZI striech a zelených stien</t>
+          <t xml:space="preserve">vážený koeficient MZI striech a zelených stien</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
@@ -1478,12 +1498,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>B-AD10 — akumulácia zrážkovej vody</t>
+          <t xml:space="preserve">B-AD10 — akumulácia zrážkovej vody</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>podiel objemu nádrží na objeme, ktorý je pre areál optimálny</t>
+          <t xml:space="preserve">podiel objemu nádrží na objeme, ktorý je pre areál optimálny</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
@@ -1495,12 +1515,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Odtok zo spevnených plôch (doplnok VESMA)</t>
+          <t xml:space="preserve">Odtok zo spevnených plôch (doplnok VESMA)</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>podiel spevnených a polopriepustných plôch a striech, z ktorých voda ide do vsaku alebo retencie namiesto kanalizácie</t>
+          <t xml:space="preserve">podiel odtokovej plochy — spevnené a polopriepustné plochy pozemkov plus strechy budov — z ktorej voda ide do vsaku alebo retencie namiesto kanalizácie, vodného toku či neriešeného odtoku</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
@@ -1509,28 +1529,47 @@
       <c r="D13" s="12" t="inlineStr"/>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>nie je to indikátor Klimaskenu — pridali sme ho my</t>
+          <t xml:space="preserve">nie je to indikátor Klimaskenu — pridali sme ho my</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Má doplnok „odtok zo spevnených plôch" v skóre vôbec byť?</t>
+          <t xml:space="preserve">Má doplnok „odtok zo spevnených plôch" v skóre vôbec byť?</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>bez neho by sa údaj o odvode vody, ktorý dotazník zbiera, do skóre nedostal</t>
+          <t xml:space="preserve">bez neho by sa údaj o odvode vody, ktorý dotazník zbiera, do skóre nedostal</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>áno, s váhou 15</t>
+          <t xml:space="preserve">áno, s váhou 15</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
       <c r="E14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je správne, že z priepustnej plochy sa odvod vody nehodnotí?</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z trávnika zrážka vsiakne tam, kde spadne, takže „neriešený" odvod na ňom nie je nedostatok. Kvalitu priepustnej plochy ocení B-GOV2.</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">áno, počíta sa len odtoková plocha</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr"/>
+      <c r="E15" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1543,7 +1582,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1556,21 +1594,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3. Parametre výpočtu akumulácie (B-AD10)</t>
+          <t xml:space="preserve">3. Parametre výpočtu akumulácie (B-AD10)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Načo to je: komponent porovnáva objem nádrží v areáli s objemom, ktorý je preň optimálny.</t>
+          <t xml:space="preserve">Načo to je: komponent porovnáva objem nádrží v areáli s objemom, ktorý je preň optimálny.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Potrebný objem sa počíta ako Vn = min(Vv; Vp), kde</t>
+          <t xml:space="preserve">Potrebný objem sa počíta ako Vn = min(Vv; Vp), kde</t>
         </is>
       </c>
     </row>
@@ -1598,89 +1636,79 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Väčšina parametrov je z metodického listu. Dva sme určili sami — sú v tabuľke označené.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Hodnota dnes</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Odkiaľ hodnota je</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Potvrdená hodnota</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Poznámka</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>(vzor) fs — koeficient odtoku strechy</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
+          <t xml:space="preserve">Väčšina parametrov je z metodického listu. Tri veci sme rozhodli sami — v tabuľke sú označené,</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jedna z nich je odchýlka od metodiky (nádrž, ktorú nie je možné inštalovať).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hodnota dnes</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Odkiaľ hodnota je</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Potvrdená hodnota</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(vzor) fs — koeficient odtoku strechy</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>NAŠE ROZHODNUTIE — metodika ho odvodzuje z materiálu krytiny, VESMA má krytinu len ako voľný text, preto typická hodnota</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAŠE ROZHODNUTIE — metodika ho odvodzuje z materiálu krytiny, VESMA má krytinu len ako voľný text, preto typická hodnota</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>súhlasím / pre bežné krytiny použite X</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>ff — účinnosť filtra mechanických nečistôt</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>metodika B-AD10</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr"/>
-      <c r="E12" s="12" t="inlineStr"/>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">súhlasím / pre bežné krytiny použite X</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Sd — spotreba vody na osobu a deň (l)</t>
+          <t xml:space="preserve">ff — účinnosť filtra mechanických nečistôt</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>140</v>
+        <v>0.9</v>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>metodika B-AD10</t>
+          <t xml:space="preserve">metodika B-AD10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr"/>
@@ -1689,15 +1717,15 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>R — koeficient využitia zrážkovej vody</t>
+          <t xml:space="preserve">Sd — spotreba vody na osobu a deň (l)</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>0.5</v>
+        <v>140</v>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>metodika B-AD10</t>
+          <t xml:space="preserve">metodika B-AD10</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
@@ -1706,15 +1734,15 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>z — koeficient optimálnej veľkosti nádrže</t>
+          <t xml:space="preserve">R — koeficient využitia zrážkovej vody</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>metodika B-AD10</t>
+          <t xml:space="preserve">metodika B-AD10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
@@ -1723,88 +1751,168 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>j — ročný úhrn zrážok (mm)</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>z Open-Meteo podľa adresy areálu</t>
-        </is>
+          <t xml:space="preserve">z — koeficient optimálnej veľkosti nádrže</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>20</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>dotazník VESMA</t>
+          <t xml:space="preserve">metodika B-AD10</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>stačí ročný priemer z Open-Meteo, alebo treba iný zdroj?</t>
-        </is>
-      </c>
+      <c r="E16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>P — plocha striech (m²)</t>
+          <t xml:space="preserve">j — ročný úhrn zrážok (mm)</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>súčet pôdorysov všetkých budov areálu</t>
+          <t xml:space="preserve">z Open-Meteo podľa adresy areálu</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>dotazník VESMA</t>
+          <t xml:space="preserve">dotazník VESMA</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr"/>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stačí ročný priemer z Open-Meteo, alebo treba iný zdroj?</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>n — počet osôb v areáli</t>
+          <t xml:space="preserve">P — plocha striech (m²)</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>počet zamestnancov</t>
+          <t xml:space="preserve">súčet pôdorysov všetkých budov areálu</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>NAŠE ROZHODNUTIE</t>
+          <t xml:space="preserve">dotazník VESMA</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>v škole to nie sú žiaci, v kultúrnom dome ani návštevníci — má sa použiť kapacita zariadenia alebo obsadenosť?</t>
-        </is>
-      </c>
+      <c r="E18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Keď nádrž nie je možné inštalovať</t>
+          <t xml:space="preserve">n — počet osôb v areáli</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>komponent sa do skóre nezapočíta</t>
+          <t xml:space="preserve">počet zamestnancov</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>NAŠE ROZHODNUTIE — odchýlka od metodiky: B-AD10 zaraďuje objekt do najhoršej kategórie, my komponent vynechávame</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="n"/>
+          <t xml:space="preserve">NAŠE ROZHODNUTIE</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>skóre má viesť k rozhodnutiu, čo spraviť — komponent, na ktorý sa nedá reagovať, doň nepatrí. Je táto odchýlka v poriadku?</t>
+          <t xml:space="preserve">v škole to nie sú žiaci, v kultúrnom dome ani návštevníci — má sa použiť kapacita zariadenia alebo obsadenosť?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Areál, kde nádrž nie je možné inštalovať</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">komponent sa do skóre nezapočíta, skóre sa normalizuje cez ostatné tri a nádrž sa ani neodporúča</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAŠA ODCHÝLKA OD METODIKY</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr"/>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metodika hovorí „ak inštalácia nie je možná alebo je vylúčená… budova je označená v najhoršej kategórii" — pozri poznámku pod tabuľkou</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POZNÁMKA K NÁDRŽI, KTORÚ NIE JE MOŽNÉ INŠTALOVAŤ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Areál má príznak „nádrž nie je možné inštalovať" s povinným dôvodom (pamiatková ochrana,</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">podložie, chýbajúci priestor). Komponent akumulácie sa potom nehodnotí — vo výsledkoch aj</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v exporte je uvedené „nehodnotí sa" spolu s dôvodom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dôvod odchýlky: Klimasken je štítok, ktorý popisuje stav objektu. VESMA k stavu navrhuje aj</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">opatrenia, takže komponent, na ktorý sa nedá reagovať, by skóre len skresľoval a nástroj by</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">navyše odporúčal nerealizovateľné opatrenie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prosíme potvrdiť, či je táto odchýlka v poriadku, alebo sa máme držať metodiky a dať najhoršiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kategóriu aj tam, kde nádrž nie je možná.</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1927,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1832,122 +1939,122 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>4. Čísla v odporúčaniach, ktoré zostali bez zdroja</t>
+          <t xml:space="preserve">4. Čísla v odporúčaniach, ktoré zostali bez zdroja</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Načo to je: odporúčania sú to, čo si samospráva odnesie — text pri opatrení číta ako výsledok</t>
+          <t xml:space="preserve">Načo to je: odporúčania sú to, čo si samospráva odnesie — text pri opatrení číta ako výsledok</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>nástroja. Prahy, od ktorých sa opatrenie zobrazí, ste revidovali v septembri 2026 a nemeníme ich.</t>
+          <t xml:space="preserve">nástroja. Prahy, od ktorých sa opatrenie zobrazí, ste revidovali v septembri 2026 a nemeníme ich.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tieto štyri čísla revíziou neprešli a zdroj nemajú.</t>
+          <t xml:space="preserve">Tieto štyri čísla revíziou neprešli a zdroj nemajú.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Číslo</t>
+          <t xml:space="preserve">Číslo</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Kde sa objaví a čo tvrdí</t>
+          <t xml:space="preserve">Kde sa objaví a čo tvrdí</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Hodnota dnes</t>
+          <t xml:space="preserve">Hodnota dnes</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Potvrdená hodnota</t>
+          <t xml:space="preserve">Potvrdená hodnota</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Poznámka</t>
+          <t xml:space="preserve">Poznámka</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>(vzor) Zádrž štrkovej strechy</t>
+          <t xml:space="preserve">(vzor) Zádrž štrkovej strechy</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>koľko zrážky zadrží strecha so štrkovým zásypom</t>
+          <t xml:space="preserve">koľko zrážky zadrží strecha so štrkovým zásypom</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>20 % ročného úhrnu</t>
+          <t xml:space="preserve">20 % ročného úhrnu</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>vzor formátu — prepíšte alebo zmažte</t>
+          <t xml:space="preserve">vzor formátu — prepíšte alebo zmažte</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Zádrž zelenej strechy</t>
+          <t xml:space="preserve">Zádrž zelenej strechy</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>veta „Potenciál zachytiť X m³ dažďovej vody ročne" pri zelenej streche — X = plocha plochých striech × 0,3</t>
+          <t xml:space="preserve">veta „Potenciál zachytiť X m³ dažďovej vody ročne" pri zelenej streche — X = plocha plochých striech × 0,3</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>0,3 m³ na m² za rok</t>
+          <t xml:space="preserve">0,3 m³ na m² za rok</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>pozri poznámku pod tabuľkou</t>
+          <t xml:space="preserve">pozri poznámku pod tabuľkou</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Nahraditeľnosť spevnenej plochy</t>
+          <t xml:space="preserve">Nahraditeľnosť spevnenej plochy</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>veta „Potenciál nahradiť až X m² priepustným povrchom" pri priepustnej dlažbe — X je polovica spevnenej plochy areálu</t>
+          <t xml:space="preserve">veta „Potenciál nahradiť až X m² priepustným povrchom" pri priepustnej dlažbe — X je polovica spevnenej plochy areálu</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>50 %</t>
+          <t xml:space="preserve">50 %</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr"/>
@@ -1956,40 +2063,40 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Minimálny objem retenčnej nádrže</t>
+          <t xml:space="preserve">Minimálny objem retenčnej nádrže</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>katalógový postup pri retenčnej nádrži: „min. 3 m³ pre rodinný dom"</t>
+          <t xml:space="preserve">katalógový postup pri retenčnej nádrži: „min. 3 m³ pre rodinný dom"</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>3 m³</t>
+          <t xml:space="preserve">3 m³</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr"/>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>výpočet B-AD10 už potrebný objem počíta — má tento údaj v katalógu vôbec zostať?</t>
+          <t xml:space="preserve">výpočet B-AD10 už potrebný objem počíta — má tento údaj v katalógu vôbec zostať?</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Minimálna plocha jazierka</t>
+          <t xml:space="preserve">Minimálna plocha jazierka</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>katalógový postup pri jazierku: „min. 30 – 50 m² plochy pozemku"</t>
+          <t xml:space="preserve">katalógový postup pri jazierku: „min. 30 – 50 m² plochy pozemku"</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>30 – 50 m²</t>
+          <t xml:space="preserve">30 – 50 m²</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr"/>
@@ -1998,35 +2105,35 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>POZNÁMKA K ZÁDRŽI ZELENEJ STRECHY</t>
+          <t xml:space="preserve">POZNÁMKA K ZÁDRŽI ZELENEJ STRECHY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Pri koeficiente 0,3 v prvom riadku tabuľky nesedia jednotky —</t>
+          <t xml:space="preserve">Pri koeficiente 0,3 v prvom riadku tabuľky nesedia jednotky —</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>z m² vyjde m³ za rok bez toho, aby do výpočtu vstúpili zrážky. Po zavedení metodiky vieme</t>
+          <t xml:space="preserve">z m² vyjde m³ za rok bez toho, aby do výpočtu vstúpili zrážky. Po zavedení metodiky vieme</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>zachytenú vodu počítať poriadne (Q = j · P · fs · ff), takže nám stačí podiel ročného úhrnu,</t>
+          <t xml:space="preserve">zachytenú vodu počítať poriadne (Q = j · P · fs · ff), takže nám stačí podiel ročného úhrnu,</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>ktorý extenzívna zelená strecha zadrží. Ak taký údaj nie je, vetu radšej zrušíme.</t>
+          <t xml:space="preserve">ktorý extenzívna zelená strecha zadrží. Ak taký údaj nie je, vetu radšej zrušíme.</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2148,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2055,130 +2161,130 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5. Ceny a návratnosť opatrení modrozelenej infraštruktúry</t>
+          <t xml:space="preserve">5. Ceny a návratnosť opatrení modrozelenej infraštruktúry</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Načo to je: pri každom odporúčanom opatrení VESMA ukáže orientačnú cenu a návratnosť.</t>
+          <t xml:space="preserve">Načo to je: pri každom odporúčanom opatrení VESMA ukáže orientačnú cenu a návratnosť.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>V nástroji nie je zaznamenané, odkiaľ tie čísla pochádzajú.</t>
+          <t xml:space="preserve">V nástroji nie je zaznamenané, odkiaľ tie čísla pochádzajú.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Druhá vec: pri viacerých opatreniach nie je zrejmé, čo má „návratnosť" znamenať. Dažďová</t>
+          <t xml:space="preserve">Druhá vec: pri viacerých opatreniach nie je zrejmé, čo má „návratnosť" znamenať. Dažďová</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>záhrada ani kvitnúca lúka nič nezarábajú — nanajvýš šetria údržbu alebo stočné. Tam, kde</t>
+          <t xml:space="preserve">záhrada ani kvitnúca lúka nič nezarábajú — nanajvýš šetria údržbu alebo stočné. Tam, kde</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>finančná návratnosť nedáva zmysel, prosím napíšte, čo tam má stáť namiesto nej (napríklad</t>
+          <t xml:space="preserve">finančná návratnosť nedáva zmysel, prosím napíšte, čo tam má stáť namiesto nej (napríklad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>životnosť, alebo „bez priamej finančnej návratnosti").</t>
+          <t xml:space="preserve">životnosť, alebo „bez priamej finančnej návratnosti").</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Opatrenie</t>
+          <t xml:space="preserve">Opatrenie</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Cena dnes</t>
+          <t xml:space="preserve">Cena dnes</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Návratnosť dnes</t>
+          <t xml:space="preserve">Návratnosť dnes</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Cena potvrdená</t>
+          <t xml:space="preserve">Cena potvrdená</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Návratnosť potvrdená / čo tam má stáť</t>
+          <t xml:space="preserve">Návratnosť potvrdená / čo tam má stáť</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Poznámka / zdroj</t>
+          <t xml:space="preserve">Poznámka / zdroj</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>(vzor) Dažďový sud 300 l</t>
+          <t xml:space="preserve">(vzor) Dažďový sud 300 l</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>50 – 300 EUR</t>
+          <t xml:space="preserve">50 – 300 EUR</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>1 – 3 roky</t>
+          <t xml:space="preserve">1 – 3 roky</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>80 – 250 EUR</t>
+          <t xml:space="preserve">80 – 250 EUR</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>2 – 4 roky pri polievaní záhrady</t>
+          <t xml:space="preserve">2 – 4 roky pri polievaní záhrady</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>cenník dodávateľov 2026</t>
+          <t xml:space="preserve">cenník dodávateľov 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Retenčná / akumulačná nádrž na dažďovú vodu</t>
+          <t xml:space="preserve">Retenčná / akumulačná nádrž na dažďovú vodu</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>2 000 – 8 000 EUR (podľa objemu)</t>
+          <t xml:space="preserve">2 000 – 8 000 EUR (podľa objemu)</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>5 – 10 rokov</t>
+          <t xml:space="preserve">5 – 10 rokov</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr"/>
@@ -2188,17 +2294,17 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Dažďová záhrada</t>
+          <t xml:space="preserve">Dažďová záhrada</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>500 – 3 000 EUR</t>
+          <t xml:space="preserve">500 – 3 000 EUR</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>3 – 5 rokov</t>
+          <t xml:space="preserve">3 – 5 rokov</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr"/>
@@ -2208,17 +2314,17 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Vsakovací rigol / jama</t>
+          <t xml:space="preserve">Vsakovací rigol / jama</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1 500 – 5 000 EUR</t>
+          <t xml:space="preserve">1 500 – 5 000 EUR</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>5 – 8 rokov</t>
+          <t xml:space="preserve">5 – 8 rokov</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
@@ -2228,17 +2334,17 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Zelená strecha (extenzívna)</t>
+          <t xml:space="preserve">Zelená strecha (extenzívna)</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>40 – 80 EUR/m²</t>
+          <t xml:space="preserve">40 – 80 EUR/m²</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>10 – 15 rokov</t>
+          <t xml:space="preserve">10 – 15 rokov</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
@@ -2248,17 +2354,17 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Zelená strecha (intenzívna)</t>
+          <t xml:space="preserve">Zelená strecha (intenzívna)</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>80 – 200 EUR/m²</t>
+          <t xml:space="preserve">80 – 200 EUR/m²</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>15 – 25 rokov</t>
+          <t xml:space="preserve">15 – 25 rokov</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
@@ -2268,17 +2374,17 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Priepustná / zatrávňovacia dlažba</t>
+          <t xml:space="preserve">Priepustná / zatrávňovacia dlažba</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>25 – 60 EUR/m²</t>
+          <t xml:space="preserve">25 – 60 EUR/m²</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>8 – 12 rokov</t>
+          <t xml:space="preserve">8 – 12 rokov</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -2288,17 +2394,17 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Výsadba stromov (tieňové)</t>
+          <t xml:space="preserve">Výsadba stromov (tieňové)</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>50 – 500 EUR/strom</t>
+          <t xml:space="preserve">50 – 500 EUR/strom</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>3 – 7 rokov</t>
+          <t xml:space="preserve">3 – 7 rokov</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
@@ -2308,17 +2414,17 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Kvitnúca lúka namiesto trávnika</t>
+          <t xml:space="preserve">Kvitnúca lúka namiesto trávnika</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>3 – 10 EUR/m²</t>
+          <t xml:space="preserve">3 – 10 EUR/m²</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>1 – 3 roky</t>
+          <t xml:space="preserve">1 – 3 roky</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
@@ -2328,17 +2434,17 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Vertikálna zeleň (zelená stena)</t>
+          <t xml:space="preserve">Vertikálna zeleň (zelená stena)</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>100 – 500 EUR/m² (modulový systém)</t>
+          <t xml:space="preserve">100 – 500 EUR/m² (modulový systém)</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>8 – 15 rokov</t>
+          <t xml:space="preserve">8 – 15 rokov</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
@@ -2348,17 +2454,17 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Dažďový sud / zásobník</t>
+          <t xml:space="preserve">Dažďový sud / zásobník</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>50 – 300 EUR</t>
+          <t xml:space="preserve">50 – 300 EUR</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>1 – 3 roky</t>
+          <t xml:space="preserve">1 – 3 roky</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
@@ -2368,17 +2474,17 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Odvedenie zrážkových vôd mimo kanalizáciu</t>
+          <t xml:space="preserve">Odvedenie zrážkových vôd mimo kanalizáciu</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>500 – 2 000 EUR</t>
+          <t xml:space="preserve">500 – 2 000 EUR</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>3 – 5 rokov</t>
+          <t xml:space="preserve">3 – 5 rokov</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr"/>
@@ -2388,17 +2494,17 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Jazierko / vytvorená mokraď</t>
+          <t xml:space="preserve">Jazierko / vytvorená mokraď</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>3 000 – 20 000 EUR (podľa veľkosti)</t>
+          <t xml:space="preserve">3 000 – 20 000 EUR (podľa veľkosti)</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>10 – 20 rokov</t>
+          <t xml:space="preserve">10 – 20 rokov</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
@@ -2408,17 +2514,17 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Podzemné vsakovanie (tunel / studňa)</t>
+          <t xml:space="preserve">Podzemné vsakovanie (tunel / studňa)</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>2 000 – 15 000 EUR (podľa systému a hĺbky)</t>
+          <t xml:space="preserve">2 000 – 15 000 EUR (podľa systému a hĺbky)</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>8 – 15 rokov</t>
+          <t xml:space="preserve">8 – 15 rokov</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr"/>
@@ -2428,94 +2534,213 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Zachytenie dažďovej vody do nádob</t>
+          <t xml:space="preserve">Zachytenie dažďovej vody do nádob</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>200 – 3 000 EUR</t>
+          <t xml:space="preserve">200 – 3 000 EUR</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>2 – 5 rokov</t>
+          <t xml:space="preserve">2 – 5 rokov</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr"/>
       <c r="F25" s="12" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Mulčovanie obrábanej pôdy</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>NÁVRH: 1 – 4 EUR/m² (pri vlastnej štiepke takmer bez nákladov)</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>NÁVRH: do 1 roka (úspora zálievky a odburiňovania)</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>nové opatrenie, zatiaľ nie je v katalógu (issue #200) — hodnoty sú náš návrh</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Krycie plodiny a zelené hnojenie</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>NÁVRH: 0,05 – 0,20 EUR/m² (osivo)</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>NÁVRH: 1 – 2 sezóny (úspora hnojív)</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>nové opatrenie, zatiaľ nie je v katalógu (issue #200) — hodnoty sú náš návrh</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPATRENIA PRE PRAVIDELNE OBRÁBANÚ PÔDU — ČAKAJÚ NA POTVRDENIE, ABY SA MOHLI PRIDAŤ</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Obmedzenie orby (minimalizačné obrábanie)</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>NÁVRH: pri službe porovnateľné s orbou; vlastná technika rádovo tisíce EUR</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>NÁVRH: 2 – 5 rokov</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>nové opatrenie, zatiaľ nie je v katalógu (issue #200) — hodnoty sú náš návrh</t>
-        </is>
-      </c>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Odkedy VESMA hodnotí pravidelne obrábanú pôdu nižšie než trávnik (koeficient 0,4 oproti 0,7),</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mala by vedieť aj poradiť, čo s ňou. Tri opatrenia sú pripravené, ale v katalógu ešte nie sú —</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bez potvrdených cien by nástroj tvrdil čísla, ktoré sme si vymysleli. Návrh je v issue #200,</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v registri chýbajúcich hodnôt je to M8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opatrenie</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navrhovaná cena</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navrhovaná návratnosť</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cena potvrdená</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Návratnosť potvrdená / čo tam má stáť</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poznámka / zdroj</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mulčovanie obrábanej pôdy</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 – 4 EUR/m² pri nakupovanom materiáli; pri vlastnej štiepke a tráve takmer bez nákladov</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">do 1 roka — úsporou zálievky a odburiňovania</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr"/>
+      <c r="E34" s="12" t="inlineStr"/>
+      <c r="F34" s="12" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Krycie plodiny a zelené hnojenie</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,05 – 0,20 EUR/m² (osivo)</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 – 2 sezóny — úsporou hnojív</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr"/>
+      <c r="E35" s="12" t="inlineStr"/>
+      <c r="F35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obmedzenie orby (minimalizačné obrábanie)</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pri službe porovnateľná s orbou; vlastná technika rádovo tisíce EUR</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 – 5 rokov</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr"/>
+      <c r="E36" s="12" t="inlineStr"/>
+      <c r="F36" s="12" t="inlineStr"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Otázka k týmto trom opatreniam</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ako to navrhujeme</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Odpoveď</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Návratnosť pri mulčovaní a krycích plodinách je skôr agronomická než finančná. Má sa pole vyplniť voľne, alebo zaviesť formuláciu „nefinančná"?</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vyplniť voľne, ako je vyššie</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr"/>
+      <c r="D39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vetrolam alebo remízka na okraji poľa — zaradiť teraz, alebo neskôr?</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neskôr; dáva zmysel len pri veľkých plochách, navrhovaný prah je 2 000 m² obrábanej pôdy</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr"/>
+      <c r="D40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Od akej plochy obrábanej pôdy sa opatrenia navrhnú?</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 m² pre mulčovanie a krycie plodiny, 500 m² pre obmedzenie orby (50 m² je zhruba 5 × 10 m — pod tým je to bežný domáci hriadok)</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr"/>
+      <c r="D41" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2528,7 +2753,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -2540,77 +2764,77 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>6. Otvorené rozhodnutia — nejde o číslo, ale o pravidlo</t>
+          <t xml:space="preserve">6. Otvorené rozhodnutia — nejde o číslo, ale o pravidlo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Tri miesta mimo skóre, kde VESMA niečo zbiera alebo počíta a nie je zrejmé, či je to tak správne.</t>
+          <t xml:space="preserve">Tri miesta mimo skóre, kde VESMA niečo zbiera alebo počíta a nie je zrejmé, či je to tak správne.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Tu nečakáme hodnotu, ale rozhodnutie — stačí veta.</t>
+          <t xml:space="preserve">Tu nečakáme hodnotu, ale rozhodnutie — stačí veta.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Otázka</t>
+          <t xml:space="preserve">Otázka</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Ako to je dnes</t>
+          <t xml:space="preserve">Ako to je dnes</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Rozhodnutie</t>
+          <t xml:space="preserve">Rozhodnutie</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Poznámka</t>
+          <t xml:space="preserve">Poznámka</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>(vzor) Otázka</t>
+          <t xml:space="preserve">(vzor) Otázka</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>stav v nástroji</t>
+          <t xml:space="preserve">stav v nástroji</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>áno / nie / inak, a ako</t>
+          <t xml:space="preserve">áno / nie / inak, a ako</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>vzor formátu — prepíšte alebo zmažte</t>
+          <t xml:space="preserve">vzor formátu — prepíšte alebo zmažte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Má voda odvedená do delenej zrážkovej kanalizácie vážiť rovnako ako voda do jednotnej stokovej siete?</t>
+          <t xml:space="preserve">Má voda odvedená do delenej zrážkovej kanalizácie vážiť rovnako ako voda do jednotnej stokovej siete?</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Pri porovnaní areálov sa tri polia (jednotná, splašková, zrážková) sčítavajú do jednej hodnoty a vážia rovnako — 7 (sucho), 5 (horúčavy), 10 (voda). V skóre podľa Klimaskenu sa všetky tri rovnako počítajú ako „nezadržané".</t>
+          <t xml:space="preserve">Pri porovnaní areálov sa tri polia (jednotná, splašková, zrážková) sčítavajú do jednej hodnoty a vážia rovnako — 7 (sucho), 5 (horúčavy), 10 (voda). V skóre podľa Klimaskenu sa všetky tri rovnako počítajú ako „nezadržané".</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr"/>
@@ -2619,12 +2843,12 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Ako má do hodnotenia vstúpiť povodňové riziko budovy?</t>
+          <t xml:space="preserve">Ako má do hodnotenia vstúpiť povodňové riziko budovy?</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>VESMA ho zisťuje na stupnici 1 – 5 a vie ho načítať z máp SVP, ale nepoužíva ho v skóre, v odporúčaniach ani pri porovnaní areálov.</t>
+          <t xml:space="preserve">VESMA ho zisťuje na stupnici 1 – 5 a vie ho načítať z máp SVP, ale nepoužíva ho v skóre, v odporúčaniach ani pri porovnaní areálov.</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr"/>
@@ -2633,12 +2857,12 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Platia váhy 15 parametrov MZI pri porovnaní areálov aj naďalej?</t>
+          <t xml:space="preserve">Platia váhy 15 parametrov MZI pri porovnaní areálov aj naďalej?</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Pochádzajú z tabuľky „MZI — spoločná dohoda" (august 2026). Zmenil sa im jeden vstup: pravidelne obrábaná pôda sa už nezapočítava do potenciálu na výsadbu stromov.</t>
+          <t xml:space="preserve">Pochádzajú z tabuľky „MZI — spoločná dohoda" (august 2026). Zmenil sa im jeden vstup: pravidelne obrábaná pôda sa už nezapočítava do potenciálu na výsadbu stromov.</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr"/>
